--- a/importer-files/Chotu_Products_Import_Template_ShopCode_Ranking.xlsx
+++ b/importer-files/Chotu_Products_Import_Template_ShopCode_Ranking.xlsx
@@ -321,6 +321,11 @@
         <t>Date/time when the evidence was actually checked, preferably ISO 8601 with timezone. Leave blank until checked; do not invent freshness.</t>
       </text>
     </comment>
+    <comment ref="AH1" authorId="0" shapeId="0">
+      <text>
+        <t>Internal Rule 804 research note: record observed bestseller-sort position, product-page merchant labels, named collection membership, source URLs, check times and uncertainty. Top/featured collection names alone do not prove sales. Preserve as plain text; do not display automatically as customer product description.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1348,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1488,6 +1493,18 @@
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>These columns store ranking evidence and priorities. Template updates alone do not collect bestseller evidence, change an active cloud worker, or update the website importer/storefront.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analysis_note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Internal Rule 804 research note: record observed bestseller-sort position, product-page merchant labels, named collection membership, source URLs, check times and uncertainty. Top/featured collection names alone do not prove sales. Preserve as plain text; do not display automatically as customer product description.</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1911,6 +1928,7 @@
     <col width="25" customWidth="1" min="31" max="31"/>
     <col width="55" customWidth="1" min="32" max="32"/>
     <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="80" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2077,6 +2095,11 @@
       <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>popularity_checked_at</t>
+        </is>
+      </c>
+      <c r="AH1" s="4" t="inlineStr">
+        <is>
+          <t>analysis_note</t>
         </is>
       </c>
     </row>
